--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.00840949336849749</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>19008971</v>
+        <v>4480511</v>
       </c>
       <c r="L2" t="n">
-        <v>11558995</v>
+        <v>2548954</v>
       </c>
       <c r="M2" t="n">
-        <v>3032083</v>
+        <v>623050</v>
       </c>
       <c r="N2" t="n">
-        <v>190473</v>
+        <v>30289</v>
       </c>
       <c r="O2" t="n">
-        <v>1770444</v>
+        <v>383547</v>
       </c>
       <c r="P2" t="n">
-        <v>698095</v>
+        <v>157383</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999949336051941</v>
+        <v>0.9999911785125732</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9395590424537659</v>
+        <v>0.8849455118179321</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8663433790206909</v>
+        <v>0.7601688504219055</v>
       </c>
       <c r="T2" t="n">
-        <v>0.835591197013855</v>
+        <v>0.7000601291656494</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7049124836921692</v>
+        <v>0.4680078625679016</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8692858219146729</v>
+        <v>0.7553855180740356</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9081134796142578</v>
+        <v>0.8243314027786255</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002015272774735009</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>19008971</v>
+        <v>4480511</v>
       </c>
       <c r="E3" t="n">
-        <v>1239954</v>
+        <v>568737</v>
       </c>
       <c r="F3" t="n">
-        <v>14060</v>
+        <v>7587</v>
       </c>
       <c r="G3" t="n">
-        <v>2313</v>
+        <v>963</v>
       </c>
       <c r="H3" t="n">
-        <v>719</v>
+        <v>435</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>40278351</v>
+        <v>10069564</v>
       </c>
       <c r="K3" t="n">
-        <v>44175085</v>
+        <v>10775215</v>
       </c>
       <c r="L3" t="n">
-        <v>50771271</v>
+        <v>12327276</v>
       </c>
       <c r="M3" t="n">
-        <v>61331965</v>
+        <v>15214535</v>
       </c>
       <c r="N3" t="n">
-        <v>65227104</v>
+        <v>16292197</v>
       </c>
       <c r="O3" t="n">
-        <v>63360633</v>
+        <v>15782212</v>
       </c>
       <c r="P3" t="n">
-        <v>64820172</v>
+        <v>16189115</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9379695057868958</v>
+        <v>0.8857810497283936</v>
       </c>
       <c r="S3" t="n">
-        <v>0.881730318069458</v>
+        <v>0.7760469317436218</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8117048740386963</v>
+        <v>0.6667059063911438</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5332973003387451</v>
+        <v>0.3389054834842682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8690805435180664</v>
+        <v>0.7526654005050659</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9028740525245667</v>
+        <v>0.8139966726303101</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -929,282 +929,282 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1154739</v>
+        <v>551598</v>
       </c>
       <c r="E4" t="n">
-        <v>11558995</v>
+        <v>2548954</v>
       </c>
       <c r="F4" t="n">
-        <v>365736</v>
+        <v>165594</v>
       </c>
       <c r="G4" t="n">
-        <v>8856</v>
+        <v>4841</v>
       </c>
       <c r="H4" t="n">
-        <v>19745</v>
+        <v>12578</v>
       </c>
       <c r="I4" t="n">
-        <v>1373</v>
+        <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>1222829</v>
+        <v>582525</v>
       </c>
       <c r="L4" t="n">
-        <v>1783284</v>
+        <v>804188</v>
       </c>
       <c r="M4" t="n">
-        <v>596585</v>
+        <v>266945</v>
       </c>
       <c r="N4" t="n">
-        <v>79735</v>
+        <v>34430</v>
       </c>
       <c r="O4" t="n">
-        <v>266221</v>
+        <v>124203</v>
       </c>
       <c r="P4" t="n">
-        <v>70636</v>
+        <v>33539</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999974370002747</v>
+        <v>0.9999955892562866</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9387636184692383</v>
+        <v>0.8853631019592285</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8739691376686096</v>
+        <v>0.7680258750915527</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8234748840332031</v>
+        <v>0.6829760670661926</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6072120666503906</v>
+        <v>0.3931287825107574</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8691831827163696</v>
+        <v>0.754023015499115</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9054861664772034</v>
+        <v>0.8191314935684204</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>40213</v>
+        <v>18855</v>
       </c>
       <c r="E5" t="n">
-        <v>469430</v>
+        <v>204011</v>
       </c>
       <c r="F5" t="n">
-        <v>3032083</v>
+        <v>623050</v>
       </c>
       <c r="G5" t="n">
-        <v>36121</v>
+        <v>14991</v>
       </c>
       <c r="H5" t="n">
-        <v>149605</v>
+        <v>68576</v>
       </c>
       <c r="I5" t="n">
-        <v>7993</v>
+        <v>5035</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1257115</v>
+        <v>577749</v>
       </c>
       <c r="L5" t="n">
-        <v>1550450</v>
+        <v>735582</v>
       </c>
       <c r="M5" t="n">
-        <v>703367</v>
+        <v>311470</v>
       </c>
       <c r="N5" t="n">
-        <v>166688</v>
+        <v>59084</v>
       </c>
       <c r="O5" t="n">
-        <v>266702</v>
+        <v>126038</v>
       </c>
       <c r="P5" t="n">
-        <v>75097</v>
+        <v>35963</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999980330467224</v>
+        <v>0.9999966025352478</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9622328281402588</v>
+        <v>0.9293205142021179</v>
       </c>
       <c r="S5" t="n">
-        <v>0.949230432510376</v>
+        <v>0.9062030911445618</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9802029728889465</v>
+        <v>0.964765191078186</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9962472319602966</v>
+        <v>0.9943034648895264</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9918841123580933</v>
+        <v>0.9847562909126282</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9977806210517883</v>
+        <v>0.9957662224769592</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>27724</v>
+        <v>12011</v>
       </c>
       <c r="E6" t="n">
-        <v>54269</v>
+        <v>18196</v>
       </c>
       <c r="F6" t="n">
-        <v>54531</v>
+        <v>17109</v>
       </c>
       <c r="G6" t="n">
-        <v>190473</v>
+        <v>30289</v>
       </c>
       <c r="H6" t="n">
-        <v>27760</v>
+        <v>10615</v>
       </c>
       <c r="I6" t="n">
-        <v>2370</v>
+        <v>1135</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>18705</v>
+        <v>12664</v>
       </c>
       <c r="F7" t="n">
-        <v>158178</v>
+        <v>74118</v>
       </c>
       <c r="G7" t="n">
-        <v>30905</v>
+        <v>12853</v>
       </c>
       <c r="H7" t="n">
-        <v>1770444</v>
+        <v>383547</v>
       </c>
       <c r="I7" t="n">
-        <v>58835</v>
+        <v>26374</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>926</v>
+        <v>580</v>
       </c>
       <c r="F8" t="n">
-        <v>4080</v>
+        <v>2537</v>
       </c>
       <c r="G8" t="n">
-        <v>1540</v>
+        <v>782</v>
       </c>
       <c r="H8" t="n">
-        <v>68392</v>
+        <v>31999</v>
       </c>
       <c r="I8" t="n">
-        <v>698095</v>
+        <v>157383</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
